--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486406_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486406_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.7359</v>
+        <v>5.4354</v>
       </c>
       <c r="E2" t="n">
-        <v>2.81</v>
+        <v>3.0336</v>
       </c>
       <c r="F2" t="n">
-        <v>2.9259</v>
+        <v>2.4019</v>
       </c>
       <c r="G2" t="n">
         <v>-0.2554</v>
@@ -610,13 +610,13 @@
         <v>1.9576</v>
       </c>
       <c r="S2" t="n">
-        <v>1.5361</v>
+        <v>1.2356</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1286</v>
+        <v>0.3521</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4075</v>
+        <v>0.8835</v>
       </c>
       <c r="V2" t="n">
         <v>3.5851</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. GONZÁLEZ PÉREZ</t>
+          <t>P. GARINO GULLOTTA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.9075</v>
+        <v>3.527</v>
       </c>
       <c r="E3" t="n">
-        <v>3.457</v>
+        <v>3.0359</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4504</v>
+        <v>0.491</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3604</v>
+        <v>0.4805</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.1671</v>
+        <v>0.1339</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5275</v>
+        <v>0.3466</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5453</v>
+        <v>1.7876</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.0667</v>
+        <v>1.2322</v>
       </c>
       <c r="L3" t="n">
-        <v>0.612</v>
+        <v>0.5554</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1849</v>
+        <v>-1.3071</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1004</v>
+        <v>-1.0983</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.08450000000000001</v>
+        <v>-0.2088</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6525</v>
+        <v>1.305</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6525</v>
+        <v>1.305</v>
       </c>
       <c r="S3" t="n">
-        <v>2.8945</v>
+        <v>0.8066</v>
       </c>
       <c r="T3" t="n">
-        <v>2.9117</v>
+        <v>-0.0769</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0172</v>
+        <v>0.8835</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.9347</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.3252</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. GARINO GULLOTTA</t>
+          <t>L. GIOVANNETTI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4345</v>
+        <v>2.6555</v>
       </c>
       <c r="E4" t="n">
-        <v>3.0359</v>
+        <v>0.8914</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3986</v>
+        <v>1.7641</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4805</v>
+        <v>0.5228</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1339</v>
+        <v>0.5108</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3466</v>
+        <v>0.012</v>
       </c>
       <c r="J4" t="n">
-        <v>1.7876</v>
+        <v>0.4456</v>
       </c>
       <c r="K4" t="n">
-        <v>1.2322</v>
+        <v>0.7117</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5554</v>
+        <v>-0.2661</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.3071</v>
+        <v>0.0772</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.0983</v>
+        <v>-0.2009</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2088</v>
+        <v>0.2781</v>
       </c>
       <c r="P4" t="n">
-        <v>1.305</v>
+        <v>1.5225</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.305</v>
+        <v>1.5225</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7141999999999999</v>
+        <v>0.6102</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0769</v>
+        <v>0.4458</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7911</v>
+        <v>0.1643</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9347</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.3252</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.3904</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>H. LOPEZ BARRANTES</t>
+          <t>S. SALIN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4745</v>
+        <v>2.6454</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.989</v>
+        <v>1.0013</v>
       </c>
       <c r="F5" t="n">
-        <v>3.4635</v>
+        <v>1.6442</v>
       </c>
       <c r="G5" t="n">
-        <v>1.3977</v>
+        <v>-0.2747</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1921</v>
+        <v>-0.0547</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2056</v>
+        <v>-0.2199</v>
       </c>
       <c r="J5" t="n">
-        <v>0.989</v>
+        <v>0.763</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9125</v>
+        <v>0.6451</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0765</v>
+        <v>0.118</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4087</v>
+        <v>-1.0377</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2796</v>
+        <v>-0.6998</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1291</v>
+        <v>-0.3379</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.305</v>
+        <v>0.87</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R5" t="n">
-        <v>0.87</v>
+        <v>1.9576</v>
       </c>
       <c r="S5" t="n">
-        <v>1.6424</v>
+        <v>0.5296</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1971</v>
+        <v>-0.1947</v>
       </c>
       <c r="U5" t="n">
-        <v>1.4453</v>
+        <v>0.7243000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>0.7395</v>
+        <v>1.5204</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.5204</v>
       </c>
       <c r="X5" t="n">
-        <v>0.7395</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. GIOVANNETTI</t>
+          <t>A. GONZÁLEZ PÉREZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.2663</v>
+        <v>2.0269</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7796999999999999</v>
+        <v>1.6689</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4867</v>
+        <v>0.3579</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5228</v>
+        <v>0.3604</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5108</v>
+        <v>-0.1671</v>
       </c>
       <c r="I6" t="n">
-        <v>0.012</v>
+        <v>0.5275</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4456</v>
+        <v>0.5453</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7117</v>
+        <v>-0.0667</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.2661</v>
+        <v>0.612</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0772</v>
+        <v>-0.1849</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2009</v>
+        <v>-0.1004</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2781</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>1.5225</v>
+        <v>0.6525</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5225</v>
+        <v>0.6525</v>
       </c>
       <c r="S6" t="n">
-        <v>0.221</v>
+        <v>1.0139</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3341</v>
+        <v>1.1236</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1131</v>
+        <v>-0.1097</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. SALIN</t>
+          <t>H. LOPEZ BARRANTES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5627</v>
+        <v>1.6268</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4425</v>
+        <v>-1.4361</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1202</v>
+        <v>3.0628</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2747</v>
+        <v>1.3977</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0547</v>
+        <v>1.1921</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2199</v>
+        <v>0.2056</v>
       </c>
       <c r="J7" t="n">
-        <v>0.763</v>
+        <v>0.989</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6451</v>
+        <v>0.9125</v>
       </c>
       <c r="L7" t="n">
-        <v>0.118</v>
+        <v>0.0765</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.0377</v>
+        <v>0.4087</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6998</v>
+        <v>0.2796</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3379</v>
+        <v>0.1291</v>
       </c>
       <c r="P7" t="n">
+        <v>-1.305</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-2.1751</v>
+      </c>
+      <c r="R7" t="n">
         <v>0.87</v>
       </c>
-      <c r="Q7" t="n">
-        <v>-1.0875</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.9576</v>
-      </c>
       <c r="S7" t="n">
-        <v>-0.5531</v>
+        <v>0.7946</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.2499</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2003</v>
+        <v>1.0446</v>
       </c>
       <c r="V7" t="n">
-        <v>1.5204</v>
+        <v>0.7395</v>
       </c>
       <c r="W7" t="n">
-        <v>1.5204</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. GARCIA CALVO</t>
+          <t>G. FILIPOVIC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1784</v>
+        <v>0.1907</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6123</v>
+        <v>-1.1979</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7907</v>
+        <v>1.3886</v>
       </c>
       <c r="G8" t="n">
-        <v>2.7173</v>
+        <v>-4.496</v>
       </c>
       <c r="H8" t="n">
-        <v>1.5236</v>
+        <v>-2.3174</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1937</v>
+        <v>-2.1786</v>
       </c>
       <c r="J8" t="n">
-        <v>4.3064</v>
+        <v>-3.8432</v>
       </c>
       <c r="K8" t="n">
-        <v>2.3724</v>
+        <v>-1.6845</v>
       </c>
       <c r="L8" t="n">
-        <v>1.934</v>
+        <v>-2.1587</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.5891</v>
+        <v>-0.6528</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8488</v>
+        <v>-0.6328</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7403</v>
+        <v>-0.0199</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.9576</v>
+        <v>0.435</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.2626</v>
+        <v>-1.0875</v>
       </c>
       <c r="R8" t="n">
-        <v>1.305</v>
+        <v>1.5225</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3664</v>
+        <v>1.2314</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.822</v>
+        <v>0.7126</v>
       </c>
       <c r="U8" t="n">
-        <v>1.1883</v>
+        <v>0.5188</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.3045</v>
+        <v>3.0202</v>
       </c>
       <c r="W8" t="n">
-        <v>0.3904</v>
+        <v>3.0202</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.695</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. FILIPOVIC</t>
+          <t>S. GARCIA CALVO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6571</v>
+        <v>-0.0704</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.645</v>
+        <v>1.0593</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9879</v>
+        <v>-1.1298</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.496</v>
+        <v>2.7173</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.3174</v>
+        <v>1.5236</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.1786</v>
+        <v>1.1937</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.8432</v>
+        <v>4.3064</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.6845</v>
+        <v>2.3724</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.1587</v>
+        <v>1.934</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6528</v>
+        <v>-1.5891</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6328</v>
+        <v>-0.8488</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0199</v>
+        <v>-0.7403</v>
       </c>
       <c r="P9" t="n">
-        <v>0.435</v>
+        <v>-1.9576</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0875</v>
+        <v>-3.2626</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5225</v>
+        <v>1.305</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3837</v>
+        <v>0.4744</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2656</v>
+        <v>-0.3749</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1181</v>
+        <v>0.8493000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>3.0202</v>
+        <v>-1.3045</v>
       </c>
       <c r="W9" t="n">
-        <v>3.0202</v>
+        <v>0.3904</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8895</v>
+        <v>-0.5928</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0997</v>
+        <v>-0.9879</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2102</v>
+        <v>0.3951</v>
       </c>
       <c r="G10" t="n">
         <v>-0.0248</v>
@@ -1234,13 +1234,13 @@
         <v>1.305</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5703</v>
+        <v>0.867</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0601</v>
+        <v>0.1719</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5102</v>
+        <v>0.6952</v>
       </c>
       <c r="V10" t="n">
         <v>-0.5649999999999999</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>L. NWOGBO</t>
+          <t>O. SILVERIO GRULLON</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3263</v>
+        <v>-2.338</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8139</v>
+        <v>-2.4503</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.5124</v>
+        <v>0.1123</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.7304</v>
+        <v>-2.3672</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1733</v>
+        <v>-0.7727000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9036999999999999</v>
+        <v>-1.5945</v>
       </c>
       <c r="J11" t="n">
-        <v>1.6659</v>
+        <v>-1.3989</v>
       </c>
       <c r="K11" t="n">
-        <v>1.5512</v>
+        <v>0.0912</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1147</v>
+        <v>-1.4901</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.3963</v>
+        <v>-0.9683</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.3779</v>
+        <v>-0.8639</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.0184</v>
+        <v>-0.1044</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.3926</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.2626</v>
+        <v>-1.0875</v>
       </c>
       <c r="R11" t="n">
         <v>0.87</v>
       </c>
       <c r="S11" t="n">
-        <v>1.341</v>
+        <v>0.2466</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1971</v>
+        <v>0.0361</v>
       </c>
       <c r="U11" t="n">
-        <v>1.1439</v>
+        <v>0.2106</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.5443</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5857</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>O. SILVERIO GRULLON</t>
+          <t>L. NWOGBO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.0008</v>
+        <v>-2.7771</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.8974</v>
+        <v>-0.9257</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1034</v>
+        <v>-1.8514</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.3672</v>
+        <v>-0.7304</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.7727000000000001</v>
+        <v>0.1733</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.5945</v>
+        <v>-0.9036999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.3989</v>
+        <v>1.6659</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0912</v>
+        <v>1.5512</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.4901</v>
+        <v>0.1147</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.9683</v>
+        <v>-2.3963</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8639</v>
+        <v>-1.3779</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1044</v>
+        <v>-1.0184</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.2175</v>
+        <v>-2.3926</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.0875</v>
+        <v>-3.2626</v>
       </c>
       <c r="R12" t="n">
         <v>0.87</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4161</v>
+        <v>0.8902</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.411</v>
+        <v>0.0853</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0052</v>
+        <v>0.8048</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-0.5443</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.5857</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="13">
@@ -1423,28 +1423,28 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>12.3293</v>
+        <v>12.3294</v>
       </c>
       <c r="E13" t="n">
-        <v>3.692399999999998</v>
+        <v>3.6925</v>
       </c>
       <c r="F13" t="n">
-        <v>8.636900000000001</v>
+        <v>8.636699999999998</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.669800000000001</v>
+        <v>-2.6698</v>
       </c>
       <c r="H13" t="n">
         <v>0.4101</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.0799</v>
+        <v>-3.079899999999999</v>
       </c>
       <c r="J13" t="n">
         <v>6.4598</v>
       </c>
       <c r="K13" t="n">
-        <v>7.651199999999999</v>
+        <v>7.651199999999998</v>
       </c>
       <c r="L13" t="n">
         <v>-1.1912</v>
@@ -1453,7 +1453,7 @@
         <v>-9.1296</v>
       </c>
       <c r="N13" t="n">
-        <v>-7.240799999999999</v>
+        <v>-7.2408</v>
       </c>
       <c r="O13" t="n">
         <v>-1.8887</v>
@@ -1468,10 +1468,10 @@
         <v>14.1377</v>
       </c>
       <c r="S13" t="n">
-        <v>8.7004</v>
+        <v>8.700100000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>2.0309</v>
+        <v>2.031</v>
       </c>
       <c r="U13" t="n">
         <v>6.6692</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.4052</v>
+        <v>4.224</v>
       </c>
       <c r="E14" t="n">
-        <v>3.9532</v>
+        <v>3.6179</v>
       </c>
       <c r="F14" t="n">
-        <v>0.452</v>
+        <v>0.6061</v>
       </c>
       <c r="G14" t="n">
         <v>1.7922</v>
@@ -1546,13 +1546,13 @@
         <v>1.5225</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7997</v>
+        <v>-0.9809</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3509</v>
+        <v>-0.6862</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4488</v>
+        <v>-0.2947</v>
       </c>
       <c r="V14" t="n">
         <v>1.8902</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. KANDE KIELI</t>
+          <t>M. LAPORNIK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
+        <v>2.5226</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.2109</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.3117</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3.5185</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.6538</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.8647</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4.4742</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.7186</v>
+      </c>
+      <c r="L15" t="n">
         <v>2.7556</v>
       </c>
-      <c r="E15" t="n">
-        <v>1.1312</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1.6244</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1.8714</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1.3838</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.4877</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2.4956</v>
-      </c>
-      <c r="K15" t="n">
-        <v>2.2661</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.2295</v>
-      </c>
       <c r="M15" t="n">
-        <v>-0.6241</v>
+        <v>-0.9556</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8823</v>
+        <v>-1.0648</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2582</v>
+        <v>0.1091</v>
       </c>
       <c r="P15" t="n">
-        <v>2.6101</v>
+        <v>0.2175</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R15" t="n">
-        <v>2.6101</v>
+        <v>2.3926</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4008</v>
+        <v>-1.2134</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6249</v>
+        <v>-1.2834</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2241</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.3252</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.7395</v>
+        <v>0.1952</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5857</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. LAPORNIK</t>
+          <t>G. KANDE KIELI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4532</v>
+        <v>2.1544</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9874000000000001</v>
+        <v>0.6842</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4658</v>
+        <v>1.4702</v>
       </c>
       <c r="G16" t="n">
-        <v>3.5185</v>
+        <v>1.8714</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6538</v>
+        <v>1.3838</v>
       </c>
       <c r="I16" t="n">
-        <v>2.8647</v>
+        <v>0.4877</v>
       </c>
       <c r="J16" t="n">
-        <v>4.4742</v>
+        <v>2.4956</v>
       </c>
       <c r="K16" t="n">
-        <v>1.7186</v>
+        <v>2.2661</v>
       </c>
       <c r="L16" t="n">
-        <v>2.7556</v>
+        <v>0.2295</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.9556</v>
+        <v>-0.6241</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.0648</v>
+        <v>-0.8823</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1091</v>
+        <v>0.2582</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2175</v>
+        <v>2.6101</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3926</v>
+        <v>2.6101</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.2828</v>
+        <v>-1.0019</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.5069</v>
+        <v>-1.0719</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2241</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-1.3252</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1952</v>
+        <v>-0.7395</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1952</v>
+        <v>-0.5857</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4595</v>
+        <v>0.552</v>
       </c>
       <c r="E17" t="n">
         <v>0.5482</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0887</v>
+        <v>0.0038</v>
       </c>
       <c r="G17" t="n">
         <v>-0.3917</v>
@@ -1780,13 +1780,13 @@
         <v>1.305</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4539</v>
+        <v>-0.3614</v>
       </c>
       <c r="T17" t="n">
         <v>-0.411</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0429</v>
+        <v>0.0496</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0131</v>
+        <v>0.2674</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0245</v>
+        <v>0.248</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0114</v>
+        <v>0.0194</v>
       </c>
       <c r="G18" t="n">
         <v>0.4396</v>
@@ -1858,13 +1858,13 @@
         <v>0.2175</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.644</v>
+        <v>-0.3897</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0.155</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5755</v>
+        <v>-0.5447</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.2656</v>
+        <v>-1.9381</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3352</v>
+        <v>0.447</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.6009</v>
+        <v>-2.3851</v>
       </c>
       <c r="G19" t="n">
         <v>1.9075</v>
@@ -1936,13 +1936,13 @@
         <v>1.0875</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0002</v>
+        <v>-0.6726</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.548</v>
+        <v>-0.4362</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4522</v>
+        <v>-0.2364</v>
       </c>
       <c r="V19" t="n">
         <v>-2.0854</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.9857</v>
+        <v>-3.2901</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1031</v>
+        <v>-0.4384</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.8825</v>
+        <v>-2.8517</v>
       </c>
       <c r="G20" t="n">
         <v>0.6614</v>
@@ -2014,13 +2014,13 @@
         <v>0.2175</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3219</v>
+        <v>-0.6264</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4026</v>
+        <v>0.0673</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7245</v>
+        <v>-0.6937</v>
       </c>
       <c r="V20" t="n">
         <v>-2.4552</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.9832</v>
+        <v>-3.9639</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.4485</v>
+        <v>-4.3367</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4653</v>
+        <v>0.3728</v>
       </c>
       <c r="G21" t="n">
         <v>-1.5583</v>
@@ -2092,13 +2092,13 @@
         <v>1.0875</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5772</v>
+        <v>-0.5579</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.6417</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1763</v>
+        <v>0.0838</v>
       </c>
       <c r="V21" t="n">
         <v>-0.7602</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B. LUGARINI</t>
+          <t>J. POWELL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.1131</v>
+        <v>-4.0112</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.0673</v>
+        <v>-2.7461</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0458</v>
+        <v>-1.2651</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.5495</v>
+        <v>-1.859</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.253</v>
+        <v>-1.6574</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.2965</v>
+        <v>-0.2016</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.8648</v>
+        <v>-1.6071</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.1397</v>
+        <v>-1.3409</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7251</v>
+        <v>-0.2661</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.6847</v>
+        <v>-0.2519</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.1134</v>
+        <v>-0.3164</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.5714</v>
+        <v>0.0645</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.435</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R22" t="n">
-        <v>1.7401</v>
+        <v>1.0875</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3683</v>
+        <v>-0.4572</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0274</v>
+        <v>-0.6165</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6591</v>
+        <v>0.1592</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.7602</v>
+        <v>-1.695</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.7602</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. POWELL</t>
+          <t>R. JOHNSON JR</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.1961</v>
+        <v>-4.3828</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.7461</v>
+        <v>-3.9162</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.45</v>
+        <v>-0.4666</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.859</v>
+        <v>-1.1626</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.6574</v>
+        <v>-1.569</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2016</v>
+        <v>0.4064</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.6071</v>
+        <v>-0.9544</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.3409</v>
+        <v>-0.4221</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.2661</v>
+        <v>-0.5323</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.2519</v>
+        <v>-0.2082</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.3164</v>
+        <v>-1.1468</v>
       </c>
       <c r="O23" t="n">
-        <v>0.0645</v>
+        <v>0.9387</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>-1.305</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.0875</v>
+        <v>-3.2626</v>
       </c>
       <c r="R23" t="n">
-        <v>1.0875</v>
+        <v>1.9576</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6422</v>
+        <v>-1.7199</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6165</v>
+        <v>-0.8292</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0257</v>
+        <v>-0.8908</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.695</v>
+        <v>-0.1952</v>
       </c>
       <c r="W23" t="n">
-        <v>0.5649999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.2599</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R. JOHNSON JR</t>
+          <t>B. LUGARINI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.8722</v>
+        <v>-4.4636</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.2515</v>
+        <v>-3.9555</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.6207</v>
+        <v>-0.5081</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.1626</v>
+        <v>-2.5495</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.569</v>
+        <v>-1.253</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4064</v>
+        <v>-1.2965</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.9544</v>
+        <v>-0.8648</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.4221</v>
+        <v>-0.1397</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.5323</v>
+        <v>-0.7251</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.2082</v>
+        <v>-1.6847</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.1468</v>
+        <v>-1.1134</v>
       </c>
       <c r="O24" t="n">
-        <v>0.9387</v>
+        <v>-0.5714</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.305</v>
+        <v>-0.435</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.2626</v>
+        <v>-2.1751</v>
       </c>
       <c r="R24" t="n">
-        <v>1.9576</v>
+        <v>1.7401</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.2093</v>
+        <v>-0.7189</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.1644</v>
+        <v>-0.9157</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.0449</v>
+        <v>0.1968</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.1952</v>
+        <v>-0.7602</v>
       </c>
       <c r="W24" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.3252</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="25">
@@ -2362,25 +2362,25 @@
         <v>-12.3293</v>
       </c>
       <c r="E25" t="n">
-        <v>-8.636800000000001</v>
+        <v>-8.636699999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.692500000000001</v>
+        <v>-3.6926</v>
       </c>
       <c r="G25" t="n">
         <v>2.6695</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.4102999999999994</v>
+        <v>-0.4102999999999992</v>
       </c>
       <c r="I25" t="n">
-        <v>3.0799</v>
+        <v>3.079899999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>9.1297</v>
+        <v>9.129700000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>7.2409</v>
+        <v>7.240899999999999</v>
       </c>
       <c r="L25" t="n">
         <v>1.8887</v>
@@ -2389,7 +2389,7 @@
         <v>-6.4599</v>
       </c>
       <c r="N25" t="n">
-        <v>-7.6512</v>
+        <v>-7.651199999999999</v>
       </c>
       <c r="O25" t="n">
         <v>1.1911</v>
@@ -2404,10 +2404,10 @@
         <v>15.2254</v>
       </c>
       <c r="S25" t="n">
-        <v>-8.700299999999999</v>
+        <v>-8.700200000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>-6.669400000000001</v>
+        <v>-6.669500000000001</v>
       </c>
       <c r="U25" t="n">
         <v>-2.0309</v>
